--- a/public/templates/examples/A-027-CybersecurityBudgetResourceAllocationRecord-EXAMPLE-S.xlsx
+++ b/public/templates/examples/A-027-CybersecurityBudgetResourceAllocationRecord-EXAMPLE-S.xlsx
@@ -521,7 +521,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="18" t="inlineStr">
         <is>
-          <t>SAMPLE — illustrative record, not an adopted document</t>
+          <t>SAMPLE: illustrative record, not an adopted document</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Indiana statutes and administrative code: IC 36-8-16.7 — allowable uses of statewide 911 fund distributions</t>
+          <t>Indiana statutes and administrative code: IC 36-8-16.7: allowable uses of statewide 911 fund distributions</t>
         </is>
       </c>
     </row>

--- a/public/templates/examples/A-027-CybersecurityBudgetResourceAllocationRecord-EXAMPLE-S.xlsx
+++ b/public/templates/examples/A-027-CybersecurityBudgetResourceAllocationRecord-EXAMPLE-S.xlsx
@@ -18,7 +18,7 @@
   <numFmts count="0"/>
   <fonts count="8">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
@@ -294,7 +294,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="666750" cy="666750"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -361,12 +361,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>

--- a/public/templates/examples/A-027-CybersecurityBudgetResourceAllocationRecord-EXAMPLE-S.xlsx
+++ b/public/templates/examples/A-027-CybersecurityBudgetResourceAllocationRecord-EXAMPLE-S.xlsx
@@ -3,11 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ledger" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Ledger!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -589,7 +592,7 @@
       <c r="E6" s="17" t="n"/>
       <c r="F6" s="16" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="34.7" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Coverage / Cycle</t>
@@ -615,7 +618,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="8" t="n"/>
     </row>
-    <row r="11" ht="27.75" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Entry #</t>
@@ -647,7 +650,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>0001</t>
@@ -679,7 +682,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>0002</t>
@@ -739,7 +742,7 @@
       </c>
       <c r="F14" s="11" t="inlineStr"/>
     </row>
-    <row r="15" ht="30" customHeight="1">
+    <row r="15" ht="34.7" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>0004</t>
@@ -771,7 +774,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
+    <row r="16" ht="34.7" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
           <t>0005</t>
@@ -803,7 +806,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
+    <row r="17" ht="34.7" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t>0006</t>
@@ -877,7 +880,7 @@
     <row r="24" ht="29.75" customHeight="1">
       <c r="A24" s="8" t="n"/>
     </row>
-    <row r="25" ht="15" customHeight="1">
+    <row r="25" ht="34.7" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
           <t>FY2026 commits about $19,000 across tooling, training, staffing time, and resilience, plus roughly 0.2 FTE of the Director's time. Tied to the Cybersecurity Charter. Two lines draw on the state 911 fund under IC 36-8-16.7; the rest is county general fund.</t>
@@ -915,7 +918,7 @@
       <c r="E28" s="12" t="n"/>
       <c r="F28" s="12" t="n"/>
     </row>
-    <row r="29" ht="34" customHeight="1">
+    <row r="29" ht="50.5" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Prepared by (Director)</t>
@@ -1069,11 +1072,11 @@
       <c r="E46" s="11" t="n"/>
       <c r="F46" s="11" t="n"/>
     </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="2" t="n"/>
+    <row r="48">
+      <c r="A48"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="28">
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="A27:F27"/>
@@ -1096,7 +1099,6 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A48:F48"/>
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A4:B4"/>
@@ -1105,7 +1107,7 @@
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;36 &amp;KBFBFBFSAMPLE</oddHeader>
     <oddFooter/>
